--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486908_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486908_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4076</v>
+        <v>4.9058</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9384</v>
+        <v>7.3181</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.5309</v>
+        <v>-2.4123</v>
       </c>
       <c r="G2" t="n">
         <v>1.3238</v>
@@ -610,13 +610,13 @@
         <v>2.2588</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.1216</v>
+        <v>-1.6233</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1121</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0095</v>
+        <v>-0.8909</v>
       </c>
       <c r="V2" t="n">
         <v>2.9466</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1453</v>
+        <v>2.1744</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1838</v>
+        <v>1.7465</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9614</v>
+        <v>0.4279</v>
       </c>
       <c r="G3" t="n">
         <v>1.4673</v>
@@ -688,13 +688,13 @@
         <v>2.4641</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0271</v>
+        <v>0.0562</v>
       </c>
       <c r="T3" t="n">
-        <v>1.685</v>
+        <v>0.2477</v>
       </c>
       <c r="U3" t="n">
-        <v>0.342</v>
+        <v>-0.1915</v>
       </c>
       <c r="V3" t="n">
         <v>0.2402</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. ORTIZ TORRES</t>
+          <t>C. HENDERSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5979</v>
+        <v>0.9028</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9479</v>
+        <v>-0.9928</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5459</v>
+        <v>1.8956</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4402</v>
+        <v>-1.236</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9506</v>
+        <v>-0.1072</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5104</v>
+        <v>-1.1288</v>
       </c>
       <c r="J4" t="n">
-        <v>0.474</v>
+        <v>-0.8028</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1714</v>
+        <v>0.0263</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6974</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0338</v>
+        <v>-0.4331</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2208</v>
+        <v>-0.1335</v>
       </c>
       <c r="O4" t="n">
-        <v>0.187</v>
+        <v>-0.2996</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4107</v>
+        <v>1.8481</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.616</v>
+        <v>1.8481</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.828</v>
+        <v>0.0504</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3952</v>
+        <v>-0.4302</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4327</v>
+        <v>0.4806</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3963</v>
+        <v>0.2402</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X4" t="n">
-        <v>1.3963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. HENDERSON</t>
+          <t>E. ORTIZ TORRES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5898</v>
+        <v>0.8961</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.543</v>
+        <v>-0.7387</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1327</v>
+        <v>1.6348</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.236</v>
+        <v>0.4402</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1072</v>
+        <v>0.9506</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1288</v>
+        <v>-0.5104</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8028</v>
+        <v>0.474</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0263</v>
+        <v>1.1714</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.6974</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4331</v>
+        <v>-0.0338</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1335</v>
+        <v>-0.2208</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2996</v>
+        <v>0.187</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8481</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8481</v>
+        <v>0.616</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2626</v>
+        <v>-0.5298</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9804</v>
+        <v>-0.186</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7178</v>
+        <v>-0.3438</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2402</v>
+        <v>1.3963</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.3963</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7169</v>
+        <v>-1.2086</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1868</v>
+        <v>-0.127</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-1.0816</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7448</v>
@@ -922,13 +922,13 @@
         <v>0.2053</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7609</v>
+        <v>0.2693</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4339</v>
+        <v>0.1201</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3271</v>
+        <v>0.1492</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9384</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1864</v>
+        <v>-1.2203</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5571</v>
+        <v>-1.7392</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3707</v>
+        <v>0.5189</v>
       </c>
       <c r="G7" t="n">
         <v>0.5474</v>
@@ -1000,13 +1000,13 @@
         <v>2.6694</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2964</v>
+        <v>-0.3303</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5538</v>
+        <v>0.3718</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8502</v>
+        <v>-0.702</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3437</v>
+        <v>-1.2896</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4323</v>
+        <v>-0.8821</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9114</v>
+        <v>-0.4075</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8462</v>
@@ -1078,13 +1078,13 @@
         <v>2.0534</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.826</v>
+        <v>-0.772</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1121</v>
+        <v>-0.5619</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7139</v>
+        <v>-0.21</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6982</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8019</v>
+        <v>-2.8456</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8034</v>
+        <v>-0.6988</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9985</v>
+        <v>-2.1467</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0372</v>
@@ -1156,13 +1156,13 @@
         <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9434</v>
+        <v>-0.987</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6587</v>
+        <v>-0.5541</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2846</v>
+        <v>-0.4328</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.94</v>
+        <v>-3.7604</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8377</v>
+        <v>-2.6285</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1022</v>
+        <v>-1.1319</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0644</v>
@@ -1234,13 +1234,13 @@
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8489</v>
+        <v>-0.6693</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3216</v>
+        <v>-0.1124</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5272</v>
+        <v>-0.5569</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.0631</v>
+        <v>-5.2075</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9301</v>
+        <v>-4.3412</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.133</v>
+        <v>-0.8663</v>
       </c>
       <c r="G11" t="n">
         <v>-5.2297</v>
@@ -1312,13 +1312,13 @@
         <v>2.0534</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8601</v>
+        <v>-1.0044</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7091</v>
+        <v>-0.1203</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.151</v>
+        <v>-0.8842</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.311399999999999</v>
+        <v>-6.652900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.742500000000001</v>
+        <v>-3.083699999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.569</v>
+        <v>-3.5691</v>
       </c>
       <c r="G12" t="n">
         <v>-7.3796</v>
@@ -1390,13 +1390,13 @@
         <v>16.4273</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.199000000000001</v>
+        <v>-5.5402</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.6165</v>
+        <v>-1.9577</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.5822</v>
+        <v>-3.5823</v>
       </c>
       <c r="V12" t="n">
         <v>3.186700000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.390000000000001</v>
+        <v>8.1365</v>
       </c>
       <c r="E13" t="n">
-        <v>7.0077</v>
+        <v>5.9617</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3823</v>
+        <v>2.1748</v>
       </c>
       <c r="G13" t="n">
         <v>5.5145</v>
@@ -1468,13 +1468,13 @@
         <v>1.2321</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8837</v>
+        <v>1.6301</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1966</v>
+        <v>1.1505</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6871</v>
+        <v>0.4796</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2402</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4364</v>
+        <v>7.4214</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6532</v>
+        <v>5.4901</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7831</v>
+        <v>1.9313</v>
       </c>
       <c r="G14" t="n">
         <v>8.004300000000001</v>
@@ -1546,13 +1546,13 @@
         <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4591</v>
+        <v>0.526</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7905</v>
+        <v>0.0464</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3314</v>
+        <v>0.4796</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6982</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7317</v>
+        <v>5.3342</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4224</v>
+        <v>3.004</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3094</v>
+        <v>2.3303</v>
       </c>
       <c r="G15" t="n">
         <v>2.9809</v>
@@ -1624,13 +1624,13 @@
         <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2848</v>
+        <v>0.8872</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6042</v>
+        <v>0.1858</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6805</v>
+        <v>0.7014</v>
       </c>
       <c r="V15" t="n">
         <v>1.8768</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8796</v>
+        <v>1.2406</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5999</v>
+        <v>0.4953</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2798</v>
+        <v>0.7453</v>
       </c>
       <c r="G16" t="n">
         <v>1.1242</v>
@@ -1702,13 +1702,13 @@
         <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1624</v>
+        <v>0.1985</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1122</v>
+        <v>0.0076</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2746</v>
+        <v>0.1909</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6982</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.6545</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6838</v>
+        <v>-0.2654</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1955</v>
+        <v>0.92</v>
       </c>
       <c r="G17" t="n">
         <v>-1.4055</v>
@@ -1780,13 +1780,13 @@
         <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2271</v>
+        <v>0.37</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.651</v>
+        <v>-0.2326</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8781</v>
+        <v>0.6026</v>
       </c>
       <c r="V17" t="n">
         <v>0.4579</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. PAZ VAZQUEZ</t>
+          <t>D. DE LA RUA DE AGUSTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1922</v>
+        <v>-0.2153</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8414</v>
+        <v>0.3787</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3508</v>
+        <v>-0.5941</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4646</v>
+        <v>-1.3833</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.609</v>
+        <v>-1.3331</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1445</v>
+        <v>-0.0502</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6077</v>
+        <v>-0.6766</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.418</v>
+        <v>-1.2287</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0257</v>
+        <v>0.5522</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0723</v>
+        <v>-0.7067</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.191</v>
+        <v>-0.1044</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8813</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4107</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.8107</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6042</v>
+        <v>0.5112</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0788</v>
+        <v>0.2995</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.5975</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. DE LA RUA DE AGUSTIN</t>
+          <t>J. RODRIGUEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7059</v>
+        <v>-1.0535</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9811</v>
+        <v>-2.0932</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7248</v>
+        <v>1.0396</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3833</v>
+        <v>-1.7906</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3331</v>
+        <v>1.3038</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0502</v>
+        <v>-3.0944</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6766</v>
+        <v>-1.1361</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2287</v>
+        <v>0.7981</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5522</v>
+        <v>-1.9342</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7067</v>
+        <v>-0.6545</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1044</v>
+        <v>0.5057</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-1.1602</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.8214</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2321</v>
+        <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6798999999999999</v>
+        <v>0.7371</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8486</v>
+        <v>0.0696</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1687</v>
+        <v>0.6675</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.5975</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ JIMENEZ</t>
+          <t>S. PAZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8049</v>
+        <v>-1.4346</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6162</v>
+        <v>-1.1552</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8112</v>
+        <v>-0.2793</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7906</v>
+        <v>-1.4646</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3038</v>
+        <v>-1.609</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.0944</v>
+        <v>0.1445</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1361</v>
+        <v>0.6077</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7981</v>
+        <v>-0.418</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9342</v>
+        <v>1.0257</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6545</v>
+        <v>-2.0723</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5057</v>
+        <v>-1.191</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1602</v>
+        <v>-0.8813</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0267</v>
+        <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0143</v>
+        <v>0.4407</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4534</v>
+        <v>0.2904</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4391</v>
+        <v>0.1502</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0126</v>
+        <v>-4.5506</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5423</v>
+        <v>-3.2285</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4703</v>
+        <v>-1.3221</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8355</v>
@@ -2092,13 +2092,13 @@
         <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1801</v>
+        <v>0.6422</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1045</v>
+        <v>0.4183</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0756</v>
+        <v>0.2238</v>
       </c>
       <c r="V21" t="n">
         <v>-2.9466</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.9221</v>
+        <v>-6.8269</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4492</v>
+        <v>-5.0183</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4729</v>
+        <v>-1.8086</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3648</v>
@@ -2170,13 +2170,13 @@
         <v>1.4374</v>
       </c>
       <c r="S22" t="n">
-        <v>2.2558</v>
+        <v>1.3511</v>
       </c>
       <c r="T22" t="n">
-        <v>2.704</v>
+        <v>1.135</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4482</v>
+        <v>0.2161</v>
       </c>
       <c r="V22" t="n">
         <v>-2.117</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.311599999999999</v>
+        <v>8.706300000000001</v>
       </c>
       <c r="E23" t="n">
         <v>3.569199999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>3.7425</v>
+        <v>5.137199999999999</v>
       </c>
       <c r="G23" t="n">
         <v>7.379599999999999</v>
@@ -2248,13 +2248,13 @@
         <v>13.3472</v>
       </c>
       <c r="S23" t="n">
-        <v>6.1988</v>
+        <v>7.5936</v>
       </c>
       <c r="T23" t="n">
         <v>3.5822</v>
       </c>
       <c r="U23" t="n">
-        <v>2.6165</v>
+        <v>4.0112</v>
       </c>
       <c r="V23" t="n">
         <v>-3.1869</v>
